--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_952_Panama_Pacific.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_952_Panama_Pacific.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R7d1b7db1613c4958"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Ra4870ea2a65c49cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rb3ad09ba5cf64ad9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rf9e8f289b56e477b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4c33d55c8ff64e05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R196c0722fb9147ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R79187566a69b4d82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R8813bc0022ef452b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra8dc1d96712241eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R236dcaf28d35409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9baed32307c74861"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rd6fd6053e43a4650"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ952CommercialTable" displayName="EEZ952CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ952CommercialTable" displayName="EEZ952CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ952FunctionalTable" displayName="EEZ952FunctionalTable" ref="A1:O16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O16"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ952FunctionalTable" displayName="EEZ952FunctionalTable" ref="A1:E16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E16"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ952ValidationTable" displayName="EEZ952ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ952ValidationTable" displayName="EEZ952ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -5183,7 +5137,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5550f0b4e3f42d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c09bbaf121f4ac0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5193,20 +5147,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5214,606 +5158,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>231378.4529</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>2.47</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>29.51209226666387</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>231378.4529</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>29.51209226666387</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$68,A2,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>6828462.250502741</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2.47</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>29.51209226666387</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>6828462.250502741</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>0.709197624</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.27</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1862.0871366628655</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>0.709197624</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1862.0871366628658</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$68,A3,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1320.5877730022676</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>1320.5877730022676</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>7249.219267546299</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>2.9340093558536244</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>85.90320271315807</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>7249.219267546299</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>111.73847655106553</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$68,A4,'Species'!$U$2:$U$68))</x:f>
-        <x:v>810016.7171402546</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>2.9340093558536244</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>85.90320271315807</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>622731.152252161</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>187285.56488809362</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3007486685237428</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.3007486685237429</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>119</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.06</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1148.1536214968817</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1148.1536214968817</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$68,A5,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>136630.28095812892</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.06</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1148.1536214968817</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>136630.28095812892</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>37597.191999999995</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.89</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>77.6247116628692</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>37597.191999999995</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$68,A6,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2918471.1883335323</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.89</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>77.6247116628692</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>2918471.1883335323</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>19.545988118</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0181417695365043</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.426577353060136</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>19.545988118</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.469736514791416</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$68,A7,'Species'!$U$2:$U$68))</x:f>
-        <x:v>204.64134551670375</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0181417695365043</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.426577353060136</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>203.7977570543213</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0.8435884623824563</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0041393412497548</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.004139341249754785</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>16252.7906495801</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.294025661289386</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>196.80025702344648</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>16252.7906495801</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>197.95242057656412</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$68,A8,'Species'!$U$2:$U$68))</x:f>
-        <x:v>3217279.2502085287</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.294025661289386</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>196.80025702344648</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3198553.377185631</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>18725.873022897635</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.005854481953143</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.005854481953142926</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>9084.749235138697</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.016673365704187</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1039.138332528325</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>9084.749235138697</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1196.8076248172226</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$68,A9,'Species'!$U$2:$U$68))</x:f>
-        <x:v>10872697.154166425</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.016673365704187</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1039.138332528325</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>9440311.171640001</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1432385.9825264234</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.1517308017165269</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.15173080171652698</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>252.1524084093</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.186004189782567</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1534.6317878285186</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>252.1524084093</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1770.292485985194</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$68,A10,'Species'!$U$2:$U$68))</x:f>
-        <x:v>446383.5139300536</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.186004189782567</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1534.6317878285186</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>386961.1013224308</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>59422.4126076228</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1535617208152138</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.15356172081521385</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1428.8118475070003</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.414614025970488</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2597.8497290049468</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1428.8118475070003</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2607.954274662798</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$68,A11,'Species'!$U$2:$U$68))</x:f>
-        <x:v>3726275.9653947316</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.414614025970488</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2597.8497290049468</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3711838.470845118</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>14437.494549613446</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.003889580503843</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0038895805038429623</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R257509e750b3472d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f8c3d84bc5342cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5823,20 +5373,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5844,876 +5384,307 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1738</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.4</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>251.18864315095797</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1738</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>253.58965635380784</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$68,A2,'Species'!$U$2:$U$68))</x:f>
-        <x:v>440738.82274291804</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.4</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>251.18864315095797</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>436565.86179636494</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>4172.960946553096</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0095586057264816</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00955860572648157</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>130.3812774809</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>130.3812774809</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$68,A3,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>320048.08427076886</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>320048.08427076886</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>2791.9856003299005</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.417978715171118</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2618.0546938745733</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>2791.9856003299005</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2635.537761532632</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$68,A4,'Species'!$U$2:$U$68))</x:f>
-        <x:v>7358383.479324808</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.417978715171118</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2618.0546938745733</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>7309571.006173914</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>48812.473150894046</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.006677884804685</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.006677884804684893</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3.7660010280000003</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.4755555555302413</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>298.9204005472208</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3.7660010280000003</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>302.26313331120826</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$68,A5,'Species'!$U$2:$U$68))</x:f>
-        <x:v>1138.3232707765114</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.4755555555302413</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>298.9204005472208</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1125.7345357510055</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>12.588735025505912</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0111826852829986</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.011182685282998494</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>245.83389557330003</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.202868454058023</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1595.395835465583</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>245.83389557330003</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1806.9328749557549</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$68,A6,'Species'!$U$2:$U$68))</x:f>
-        <x:v>444205.3476898358</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.202868454058023</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1595.395835465583</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>392202.3732139239</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>52002.974475911935</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1325921973642605</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.13259219736426045</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>0.709197624</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.27</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>1862.0871366628655</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>0.709197624</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>1862.0871366628658</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$68,A7,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1320.5877730022676</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.27</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>1862.0871366628655</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>1320.5877730022676</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>16543.7311105214</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.3336758959502135</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>215.61347345031842</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>16543.7311105214</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>232.89209053384045</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$68,A8,'Species'!$U$2:$U$68))</x:f>
-        <x:v>3852904.1235590624</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.3336758959502135</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>215.61347345031842</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>3567051.3285676125</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>285852.7949914499</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0801370007496465</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.08013700074964639</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>97.4666858697</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.044715729242424</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1108.449034006351</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>97.4666858697</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1115.6086444807963</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$68,A9,'Species'!$U$2:$U$68))</x:f>
-        <x:v>108734.67730513161</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.044715729242424</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1108.449034006351</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>108036.85380006942</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>697.8235050621879</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0064591246460541</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0064591246460542475</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>5461.9502675289</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.020970349369804</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1049.4707755841118</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>5461.9502675289</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1049.759438738831</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$68,A10,'Species'!$U$2:$U$68))</x:f>
-        <x:v>5733733.847260546</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.020970349369804</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1049.4707755841118</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>5732157.183465403</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>1576.6637951433659</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0002750559247906</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.0002750559247906364</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>19.545988118</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.0181417695365043</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>10.426577353060136</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>19.545988118</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>10.469736514791416</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$68,A11,'Species'!$U$2:$U$68))</x:f>
-        <x:v>204.64134551670375</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.0181417695365043</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>10.426577353060136</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>203.7977570543213</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>0.8435884623824563</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0041393412497548</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.004139341249754785</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>7249.219267546299</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>2.9340093558536244</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>85.90320271315807</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>7249.219267546299</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>111.73847655106553</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$68,A12,'Species'!$U$2:$U$68))</x:f>
-        <x:v>810016.7171402546</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>2.9340093558536244</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>85.90320271315807</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>622731.152252161</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>187285.56488809362</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3007486685237428</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.3007486685237429</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>2.836790495</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.78</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>602.5595860743575</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>2.836790495</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>602.5595860743575</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$68,A13,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1709.3353064468718</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.78</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>602.5595860743575</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
-        <x:v>1709.3353064468718</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>268975.6449</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.5287072507842514</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>33.78370302562372</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>268975.6449</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>36.23723420185495</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$68,A14,'Species'!$U$2:$U$68))</x:f>
-        <x:v>9746933.438836273</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.5287072507842514</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>33.78370302562372</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>9086993.308427222</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>659940.1304090507</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0726246964215354</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.07262469642153542</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>119</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>4.06</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>1148.1536214968817</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>1148.1536214968817</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$68,A15,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>136630.28095812892</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>4.06</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>1148.1536214968817</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>136630.28095812892</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>2.552511808</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.61</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>407.3802778041126</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>2.552511808</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$68,A16,'Species'!$U$2:$U$68))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1039.8429694413178</x:v>
       </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.61</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>407.3802778041126</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>1039.8429694413178</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G16">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O16">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R90e5c62d5fef4cd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa8a15f1b3114251"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6888,7 +5859,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6987,7 +5958,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>28957741.54975291</x:v>
+        <x:v>27245483.3785698</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7001,7 +5972,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>28957741.549752906</x:v>
+        <x:v>27717386.731267262</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7015,7 +5986,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-1712258.171183113</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7029,7 +6000,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-1240354.8184856512</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -7040,9 +6011,9 @@
         <x:v>EEZ_952</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -7054,47 +6025,19 @@
         <x:v>EEZ_952</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_952</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_952</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b1f82de3f1f484d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18e02d80d1b64497"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7141,7 +6084,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
